--- a/docs/IAP审核测试场景.xlsx
+++ b/docs/IAP审核测试场景.xlsx
@@ -11,7 +11,7 @@
     <sheet name="测试统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IAP 审核测试场景'!$A$1:$J$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IAP 审核测试场景'!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>App Store Connect 后台创建 4 个 IAP 产品</t>
+          <t>App Store Connect 后台已创建 4 个 IAP（nomad.iap.month/year/forever.vip/forever.svip）；待审核通过</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Sandbox Tester 中国+美国各一个</t>
+          <t>Sandbox Tester 中国+美国各一个；KEY_ID=LGB4Z64FR5、ISSUER_ID=ed6c272c-... 已配、AuthKey.p8 已上传</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>服务端 verifyAndActivate 月卡流程已测（IAPVerifyFlowTest.testNormalPurchaseMonthly）；真机支付需 Sandbox Tester</t>
+          <t>服务端 verifyAndActivate 月卡流程已测（IAPVerifyFlowTest.testNormalPurchaseMonthly）+ 全产品矩阵覆盖；真机支付需 Sandbox Tester</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>服务端逻辑同 3.1.1；真机年卡支付需手测</t>
+          <t>服务端逻辑同 3.1.1；全产品矩阵已验证 nomad.iap.year；真机年卡支付需手测</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>服务端永久方案 expireTime=null 已测（testPurchaseLifetime）</t>
+          <t>服务端永久方案 expireTime=null 已测（testPurchaseLifetime）+ 全产品矩阵覆盖 nomad.iap.forever.vip</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>服务端逻辑同 3.1.1；真机创始人 planId=4 需手测</t>
+          <t>全产品矩阵已验证 nomad.iap.forever.svip（planId=4）；真机创始人 planId=4 需手测</t>
         </is>
       </c>
     </row>
@@ -5100,57 +5100,161 @@
     <row r="89" ht="38" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>FRAUD.2</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>支付安全</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>跨 planId 套用 productId</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>客户端传 planId=year，Apple 返回 productId=nomad.iap.month</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>拒绝激活 + 落 PENDING_VERIFY</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>MembershipServiceImpl.java</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>AUTO_PASS</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>本轮新增：跨产品套用拦截（testFraudCrossProductId）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="38" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
           <t>IDEMPOTENT.1</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>幂等</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>同一 transactionId 重复提交</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>第二次提交相同 appleTransactionId</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>不重复激活，返回已有信息</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>MembershipServiceImpl.java:216</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>AUTO_PASS</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>uk_apple_txn 唯一索引兜底</t>
         </is>
       </c>
     </row>
+    <row r="91" ht="38" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>MATRIX.1</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>全产品矩阵</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>4 个 ASC productId 全部能正确激活</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>循环测 nomad.iap.month / nomad.iap.year / nomad.iap.forever.vip / nomad.iap.forever.svip</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>4 个产品全部激活成功 + durationDays 落库正确 + 永久产品 expireTime=null</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>MembershipServiceImpl.java</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>AUTO_PASS</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>本轮新增：4 产品矩阵（testAllProductsMatrix），防 SQL 改坏无人发现</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J89"/>
+  <autoFilter ref="A1:J91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5193,11 +5297,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>26 个服务端 mock 测试已验证</t>
+          <t>49 个服务端 mock 测试已验证（含 IAP 19 + 兑换码 9 + 集成等）</t>
         </is>
       </c>
     </row>

--- a/docs/IAP审核测试场景.xlsx
+++ b/docs/IAP审核测试场景.xlsx
@@ -850,17 +850,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>不强制注册登录才能购买</t>
+          <t>已登录才能购买（V1 决策）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>匿名进购买页</t>
+          <t>未登录点击购买 → 跳登录页；登录后回到购买流程</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>商品展示不强制登录</t>
+          <t>未登录无法看到商品价格；登录态下正常购买</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MembershipCenterViewController.m</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>需结合实际业务在真机确认</t>
+          <t>V1 决策：必须登录才能购买。预期：未登录点购买 → 跳登录页；登录后回到购买流程。需真机确认跳转链路</t>
         </is>
       </c>
     </row>
@@ -3886,22 +3886,22 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>SCOPE_OUT</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>简体中文，需真机切语言</t>
+          <t>V1 不做多语言切换，文案默认简体中文</t>
         </is>
       </c>
     </row>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>SCOPE_OUT</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>繁体中文，需真机</t>
+          <t>V1 不做多语言切换</t>
         </is>
       </c>
     </row>
@@ -3990,22 +3990,22 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>SCOPE_OUT</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>英文，需真机</t>
+          <t>V1 不做多语言切换</t>
         </is>
       </c>
     </row>
@@ -4042,22 +4042,22 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>SCOPE_OUT</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>美国 App Store 账号，需美区 Sandbox Tester</t>
+          <t>V1 不做多语言切换；如需美区测试可单独用美区 Sandbox Tester</t>
         </is>
       </c>
     </row>
@@ -4094,22 +4094,22 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>SCOPE_OUT</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>货币格式，需多地区真机</t>
+          <t>V1 不做多语言切换；价格 locale 跟随 SKProduct.price 由系统保证</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>提交前确认场景 3.1/4.1-4.4/5.1-5.2/6.1-6.2/7.1-7.9/9.1-9.3 全通过</t>
+          <t>提交前确认场景 3.1/4.1-4.4/5.1-5.2/6.1-6.2/7.1-7.9 全通过（第九章多语言 V1 范围外）</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -5353,13 +5353,28 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>SCOPE_OUT（V1 范围外）</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>本版本不做：多语言切换；后续版本再测</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>CHECKLIST（N/A 提交清单）</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>非测试范畴</t>
         </is>

--- a/docs/IAP审核测试场景.xlsx
+++ b/docs/IAP审核测试场景.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>CONFIG_REQUIRED</t>
+          <t>需后台配置</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>CONFIG_REQUIRED</t>
+          <t>需后台配置</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>CONFIG_REQUIRED</t>
+          <t>需后台配置</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>CONFIG_REQUIRED</t>
+          <t>需后台配置</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>CONFIG_REQUIRED</t>
+          <t>需后台配置</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>SCOPE_OUT</t>
+          <t>V1 范围外</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>SCOPE_OUT</t>
+          <t>V1 范围外</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>SCOPE_OUT</t>
+          <t>V1 范围外</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>SCOPE_OUT</t>
+          <t>V1 范围外</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>SCOPE_OUT</t>
+          <t>V1 范围外</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>CHECKLIST</t>
+          <t>提交清单</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>CHECKLIST</t>
+          <t>提交清单</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>CHECKLIST</t>
+          <t>提交清单</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>CHECKLIST</t>
+          <t>提交清单</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>CHECKLIST</t>
+          <t>提交清单</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>CHECKLIST</t>
+          <t>提交清单</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr"/>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -5293,7 +5293,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PASS（自动化已测通过）</t>
+          <t>自动化已测</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -5308,7 +5308,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AUTO_PARTIAL（部分自动化）</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -5323,7 +5323,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MANUAL_REQUIRED（必须真机手测）</t>
+          <t>真机手测</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -5338,7 +5338,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CONFIG_REQUIRED（需配置才能测）</t>
+          <t>需后台配置</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -5353,7 +5353,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SCOPE_OUT（V1 范围外）</t>
+          <t>V1 范围外</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -5368,7 +5368,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CHECKLIST（N/A 提交清单）</t>
+          <t>提交清单</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">

--- a/docs/IAP审核测试场景.xlsx
+++ b/docs/IAP审核测试场景.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>切换地区/语言查看价格</t>
+          <t>用中国/美国 Sandbox Tester 账号查看商品价格</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>以 SKProduct.price locale 化展示</t>
+          <t>价格数字与货币符号跟随 App Store 账号地区（不可硬编码 ¥33）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -665,19 +665,19 @@
           <t>buildPlanData</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>真机手测</t>
+          <t>部分自动化</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>切换地区/语言看价格需真机手测</t>
+          <t>服务端 price 走 SKProduct.price（locale 化），未硬编码；美区 Sandbox Tester 真机确认 $ 符号</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>

--- a/docs/IAP审核测试场景.xlsx
+++ b/docs/IAP审核测试场景.xlsx
@@ -642,17 +642,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>价格由 SKProduct 提供</t>
+          <t>价格由 SKProduct 提供（防硬编码）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>用中国/美国 Sandbox Tester 账号查看商品价格</t>
+          <t>代码检查 buildPlanData 价格源；Sandbox 购买看实际显示</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>价格数字与货币符号跟随 App Store 账号地区（不可硬编码 ¥33）</t>
+          <t>价格必须来自 SKProduct.price，不可在代码里硬编码 ¥33/¥268 等</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>服务端 price 走 SKProduct.price（locale 化），未硬编码；美区 Sandbox Tester 真机确认 $ 符号</t>
+          <t>代码已确认价格走 SKProduct.price，未硬编码；Sandbox 购买真机确认显示正确。仅中国上架不涉跨区，保留为防改坏硬编码</t>
         </is>
       </c>
     </row>

--- a/docs/IAP审核测试场景.xlsx
+++ b/docs/IAP审核测试场景.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +38,17 @@
       <name val="PingFang SC"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +95,42 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +189,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,12 +676,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1370</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:agreementAttrText + :shouldInteractWithURL</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -625,7 +691,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>订阅条款 tap 手势未补，阻塞 5；按用户要求暂 pass</t>
+          <t>三条条款链接用 NSLinkAttributeName + UITextView delegate 应用内 SFSafariViewController 打开；itms-apps:// 分支已补 UIApplication openURL。真机确认点击响应。</t>
         </is>
       </c>
     </row>
@@ -662,12 +728,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>buildPlanData</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:applySKProductPrices / preloadAppStorePrices</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>代码缺陷（已修复）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -677,7 +743,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>代码已确认价格走 SKProduct.price，未硬编码；Sandbox 购买真机确认显示正确。仅中国上架不涉跨区，保留为防改坏硬编码</t>
+          <t>原代码展示价=服务端数据库价/硬编码价，与实际扣款价(SKProduct.price)不一致是审核必拒项。本轮已改：payPrice 统一用 SKProduct.price；进入页面预拉全量商品刷新卡片价。仍需服务端调整：详见末尾说明。</t>
         </is>
       </c>
     </row>
@@ -714,12 +780,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:643</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:restoreBtn (setupUI) + onTapRestore</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -729,7 +795,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>服务端 getPlans 已测；UI 入口需真机确认</t>
+          <t>恢复购买按钮与支付按钮同屏可见；服务端 getPlans 已测；真机确认 UI 入口可见。</t>
         </is>
       </c>
     </row>
@@ -766,12 +832,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2191</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:isAppStoreSandbox + submitPurchaseVerification 成功分支</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -781,7 +847,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>isAppStoreSandbox 逻辑已在客户端代码；沙箱成功提示需真机确认</t>
+          <t>通过 appStoreReceiptURL 文件名 sandboxReceipt 判沙箱，成功文案含"测试环境不会真实扣款"。真机确认显示。</t>
         </is>
       </c>
     </row>
@@ -821,9 +887,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -833,7 +899,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>代码静态检查：无外部支付入口</t>
+          <t>代码静态检查：无任何"官网/支付宝/微信支付"入口或外部跳转。</t>
         </is>
       </c>
     </row>
@@ -870,12 +936,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>ProfileViewController.m:openMembershipCenter / StampAlbumMainPageViewController.m:presentStampUnlockDialog / MembershipCenterViewController.m:onTapPay+onTapRestore+onTapRedeemDialogConfirm+onRedeemGiftCode</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>代码缺陷（已修复）</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -885,7 +951,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>V1 决策：必须登录才能购买。预期：未登录点购买 → 跳登录页；登录后回到购买流程。需真机确认跳转链路</t>
+          <t>IAP 支付硬约束：必须登录态。原代码 iOS 端无任何登录拦截，未登录可进入并点支付。本轮已加：入口拦截(弹提示+跳登录页) + 4 个 IAP 触发点兜底拦截；服务端 AuthInterceptor 已 401 兜底。</t>
         </is>
       </c>
     </row>
@@ -925,9 +991,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -937,7 +1003,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>代码静态检查：仅会员订阅</t>
+          <t>代码静态检查：仅 4 个会员订阅 IAP，无实体商品。</t>
         </is>
       </c>
     </row>
@@ -977,7 +1043,7 @@
           <t>App Store Connect</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>待配置</t>
         </is>
@@ -989,7 +1055,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>App Store Connect 配置项：商品名需含「连续包月/年」</t>
+          <t>产品名需含「连续包月/连续包年」；ASC 后台配置。</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1092,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:subscriptionInfoTextForPlan</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1041,7 +1107,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>续期条款文案需真机 UI 确认</t>
+          <t>订阅信息标签文案含"¥X/月，按月自动续期，到期前24小时内扣费，可随时取消"，满足 3.1.2。真机确认 UI 显示。</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1144,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1370</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:agreementAttrText (3条 NSLinkAttributeName)</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1093,7 +1159,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>同 1.1，订阅条款 tap 手势暂 pass</t>
+          <t>同 1.1，链接应用内 SFSafariViewController 打开。真机确认可点。</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1196,10 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+          <t>App Store Connect</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>待配置</t>
         </is>
@@ -1145,7 +1211,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>App Store Connect 后台已创建 4 个 IAP（nomad.iap.month/year/forever.vip/forever.svip）；待审核通过</t>
+          <t>4 个 IAP（nomad.iap.month/year/forever.vip/forever.svip）需 ASC 后台已创建并可供出售/准备提交。</t>
         </is>
       </c>
     </row>
@@ -1182,10 +1248,10 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
+          <t>App Store Connect</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>待配置</t>
         </is>
@@ -1197,7 +1263,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>提审时勾选「将 IAP 加入审核」</t>
+          <t>提审时勾选「将 IAP 加入审核」。</t>
         </is>
       </c>
     </row>
@@ -1234,10 +1300,10 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
+          <t>App Store Connect</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>待配置</t>
         </is>
@@ -1249,7 +1315,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>付费 App 协议需 Active</t>
+          <t>Paid Applications Agreement 必须 Active。</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1352,10 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
+          <t>App Store Connect</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>待配置</t>
         </is>
@@ -1301,7 +1367,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Sandbox Tester 中国+美国各一个；KEY_ID=LGB4Z64FR5、ISSUER_ID=ed6c272c-... 已配、AuthKey.p8 已上传</t>
+          <t>Sandbox Tester 中国+美国各一个；KEY_ID=LGB4Z64FR5、ISSUER_ID=ed6c272c-... 已配；AuthKey.p8 已上传到 fc-mono（部署 docker-compose 挂载宿主机 p8）。</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1404,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2030</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapPay + submitPurchaseVerification</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1353,7 +1419,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>服务端 verifyAndActivate 月卡流程已测（IAPVerifyFlowTest.testNormalPurchaseMonthly）+ 全产品矩阵覆盖；真机支付需 Sandbox Tester</t>
+          <t>服务端 verifyAndActivate 月卡流程 + 全产品矩阵已测；客户端 SK2 JWS 上报链路正确。真机需 SandboxTester。</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1456,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2030</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapPay</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1405,7 +1471,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>服务端逻辑同 3.1.1；全产品矩阵已验证 nomad.iap.year；真机年卡支付需手测</t>
+          <t>同 3.1.1，planId 路由正确。</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1508,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2030</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapPay + MembershipServiceImpl:246(isLifetime)</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1457,7 +1523,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>服务端永久方案 expireTime=null 已测（testPurchaseLifetime）+ 全产品矩阵覆盖 nomad.iap.forever.vip</t>
+          <t>服务端永久方案 expireTime=null 已测；客户端 isPurchasedPlanLifetime 文案适配正确。</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1560,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2030</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapPay</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1509,7 +1575,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>全产品矩阵已验证 nomad.iap.forever.svip（planId=4）；真机创始人 planId=4 需手测</t>
+          <t>全产品矩阵已测 nomad.iap.forever.svip(planId=4)。</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1612,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipServiceImpl.java:264 (existingMembership != nil 分支叠加)</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>代码缺陷</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1561,7 +1627,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>已是会员再次购买：当前无拦截（直接叠加时长），用例建议补拦截</t>
+          <t>当前行为：已是会员再购买直接叠加时长，不拦截。建议：购买前 getStatus 检查已是会员时弹"您已是会员"提示，避免用户重复付费（产品决策）。</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1664,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1856</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:fetchProductAndPay</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1613,7 +1679,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>SKProductsRequest 客户端流程，需真机</t>
+          <t>未缓存时 HUD→SKProductsRequest→缓存→startPaymentWithProduct 链路完整。真机需 SandboxTester。</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1716,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1847</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onTapPay:2033(skProducts 缓存命中)</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1665,7 +1731,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>skProducts 缓存命中，需真机</t>
+          <t>缓存命中直接 startPaymentWithProduct。真机确认。</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1768,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1897</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:productsRequest:didReceiveResponse (count==0)</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1717,7 +1783,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>invalid productID 客户端 toast，需真机</t>
+          <t>invalid productID → response.products.count==0 → 提示"未找到对应商品"+复位 payInFlight。真机确认。</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1820,12 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1990</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:paymentQueue SKPaymentTransactionStateFailed</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1769,7 +1835,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>SKErrorPaymentCancelled 客户端分支，需真机 Apple 取消面板</t>
+          <t>SKErrorPaymentCancelled → "支付已取消，可重试" + payInFlight 复位。真机 Apple 取消面板。</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1872,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1992</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:paymentQueue Failed 分支</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1821,7 +1887,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>支付失败分支，需真机</t>
+          <t>显示 transaction.error.localizedDescription。真机确认。</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1924,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2008</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:paymentQueue SKPaymentTransactionStateDeferred</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1873,7 +1939,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Deferred 家长审批，需 Sandbox Tester 开 Ask to Buy</t>
+          <t>Deferred → "购买待审批，请等待家长确认"。真机开 Ask to Buy。</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1976,12 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1885</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onTapPay (canMakePayments)</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1925,7 +1991,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>canMakePayments=NO，需真机设置关闭 IAP</t>
+          <t>canMakePayments=NO → "当前设备不支持应用内购买，请检查家长控制设置"。真机关 IAP。</t>
         </is>
       </c>
     </row>
@@ -1962,12 +2028,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1955</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:request:didFailWithError</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1977,7 +2043,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>拉商品失败分支，需真机模拟网络异常</t>
+          <t>拉商品失败 → 显示错误 + payInFlight 复位。真机模拟网络异常。</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2080,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2075</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:submitPurchaseVerification failure 分支</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2029,7 +2095,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>服务端验证失败落 PENDING_VERIFY 已测（testVerifyFailed_recordsPendingVerify）</t>
+          <t>服务端验证失败 finish + 落 PENDING_VERIFY（MembershipServiceImpl.recordPendingVerifyTxn）。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2132,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1822</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onTapPay (payInFlight 拦截)</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2081,7 +2147,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>payInFlight 拦截，需真机</t>
+          <t>payInFlight 拦截连点。真机确认。</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2184,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1812</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:updatePayButtonState (侧滑手势禁用)</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2133,7 +2199,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>侧滑手势禁用，需真机</t>
+          <t>payInFlight/restoreInFlight 时禁用 interactivePopGestureRecognizer。真机确认。</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2236,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2050</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:viewWillDisappear (isMovingFromParent)</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2185,7 +2251,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>pop 拦截提示，需真机</t>
+          <t>pop 时检测 payInFlight，提示用户。注意：当前为 toast 提示，VC 已 pop 无法回滚（如需硬拦截需自定义 leftBarButtonItem）。</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2288,12 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2100</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapRestore + handleRestoredTransaction</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2237,7 +2303,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>restore 命中本地跳过 Apple 已测（testRestoreHitLocal）</t>
+          <t>restore 命中本地跳过 Apple 已测；多笔逐笔 verifyPurchase。真机确认。</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2340,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2056</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:paymentQueueRestoreCompletedTransactionsFinished (count==0)</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2289,7 +2355,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>restore 无购买记录抛错已测（testRestoreNoHistory）</t>
+          <t>restoreTotalCount==0 → "暂无可恢复的购买记录"。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2392,12 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2069</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:restoreCompletedTransactionsFailedWithError</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2341,7 +2407,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>restore 网络失败分支，需真机关网络</t>
+          <t>网络失败 → 显示 error.localizedDescription + 复位 restoreInFlight。真机关网络。</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2444,12 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2218</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:finishOneRestore</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2393,7 +2459,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>多笔 restore 收尾，需真机多次购买</t>
+          <t>多笔 restore 用 restoreTotalCount/restoreProcessedCount 收尾 HUD 不闪烁。真机多次购买。</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2496,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2037</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onTapRestore (restoreInFlight 拦截)</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2445,7 +2511,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>restoreInFlight 拦截，需真机</t>
+          <t>restoreInFlight 拦截连点。真机确认。</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2551,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="15" t="inlineStr">
         <is>
           <t>待手测</t>
         </is>
@@ -2497,7 +2563,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>换设备恢复，需多台真机</t>
+          <t>换设备恢复：依赖 Apple 同步历史订阅，需多台真机 + 同一 Apple ID 验证。</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2600,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2209</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:handleRestoredTransaction failure 分支</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2549,7 +2615,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>restore 跨账号事务不泄露已测（testRestoreCrossUserTransaction）</t>
+          <t>服务端未识别也 finish，避免事务堆积。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2652,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2076</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:submitPurchaseVerification failure + MembershipServiceImpl.recordPendingVerifyTxn</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2601,7 +2667,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>服务端 PENDING_VERIFY 落库已测；客户端 finish 策略已在代码注释</t>
+          <t>服务端 PENDING_VERIFY 落库已测；客户端 finish 策略见 6.6 注。</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2704,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>PNIAPObserver.m:52</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>PNIAPObserver.m:resumePendingTransactions + start</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2653,7 +2719,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>PNIAPObserver.resumePendingTransactions 需真机杀进程重启</t>
+          <t>App 启动 SceneDelegate 已登录分支调用 start→resumePendingTransactions 上报。真机杀进程重启。</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2756,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:186</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:viewWillAppear + viewDidLoad</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2705,7 +2771,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>进入会员中心兜底，需真机</t>
+          <t>viewDidLoad/viewWillAppear 均调 resumePendingTransactions。真机确认。</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2808,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>PNIAPObserver.m:83</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>PNIAPObserver.m:handleTransactions (!loggedIn 分支)</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2757,7 +2823,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>未登录残留分支，需真机</t>
+          <t>未登录保留事务不 finish，等下次登录后补单（正确安全设计）。真机确认。</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2860,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>PNIAPObserver.m:79</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>PNIAPObserver.m:handleTransactions (isMembershipCenterActive continue)</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2809,7 +2875,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>VC 激活时 observer continue，需真机</t>
+          <t>VC 激活时 observer continue 由 VC 处理，避免双重上报。真机确认。</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2912,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>PNIAPObserver.m:113</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>PNIAPObserver.m:uploadTransaction failure / MembershipCenterViewController.m:submitPurchaseVerification failure</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>代码缺陷</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2861,7 +2927,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>兜底上报失败重试，需真机</t>
+          <t>当前实现：上报失败仍 finish（防队列堆积），靠 PENDING_VERIFY 客服对账。与表格预期"保留事务下次重试"不符。这是产品策略取舍：若要"自动重试"需改为不 finish，但风险是堆积超 Apple 阈值(约50笔)拒绝新支付。需产品决策。</t>
         </is>
       </c>
     </row>
@@ -2898,12 +2964,12 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2246</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:currentReceiptBase64 + refreshAppStoreReceiptIfNeeded</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2913,7 +2979,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>receipt 为空触发刷新，需真机首次安装</t>
+          <t>receipt 为空触发 SKReceiptRefreshRequest，下次调用可拿到。真机首装。</t>
         </is>
       </c>
     </row>
@@ -2950,12 +3016,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1718</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapRedeemDialogConfirm + MembershipServiceImpl.redeemCode (GIFT_CODE)</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2965,7 +3031,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>免费 GIFT_CODE 激活已测（InviteCodeRedeemPropertyTest.freeCodeDirectActivation）</t>
+          <t>免费 GIFT_CODE 直接激活已测。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3068,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1747</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapRedeemDialogConfirm (needPayment 分支)</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3017,7 +3083,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>付费 EXCHANGE_CODE 服务端处理在 redeemCode→needPayment=true 分支；返回折扣价由代码逻辑保证，未单测。客户端折扣应用需真机</t>
+          <t>EXCHANGE_CODE needPayment=true 应用折扣切订阅 tab。真机确认折扣应用。</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3120,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1755</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapRedeemDialogConfirm + MembershipServiceImpl.redeemInviteCode</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3069,7 +3135,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>付费 INVITE_CODE 同 7.2，服务端 needPayment=true 分支；客户端文案变化需真机</t>
+          <t>付费 INVITE_CODE needPayment=true 走 IAP。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3172,12 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1718</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipServiceImpl.redeemInviteCode (isFreeCode)</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3121,7 +3187,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>免费邀请码直接激活已测（InviteCodeRedeemPropertyTest.freeCodeDirectActivation）</t>
+          <t>免费邀请码直接激活。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3224,12 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1613</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:isRedeemCodeReadyToSubmit</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3173,7 +3239,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>客户端 isRedeemCodeReadyToSubmit 格式校验，需真机</t>
+          <t>格式校验拦截 → "兑换码格式不正确"。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3210,12 +3276,12 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1696</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onTapRedeemDialogConfirm (code.length==0)</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3225,7 +3291,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>客户端空码提示，需真机</t>
+          <t>空码 → "请输入兑换码"。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3328,12 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1763</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapRedeemDialogConfirm failure</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3277,7 +3343,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>码失效/已使用已测（disabledInviteCodeShouldBeRejected / usedUpInviteCodeShouldBeRejected）</t>
+          <t>码失效/已使用 failure 回调 helpLabel 显示错误。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3380,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1896</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onRedeemGiftCode (needPayment 识别)</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3329,7 +3395,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>付费码误入礼包 tab 客户端识别，需真机</t>
+          <t>礼包入口误输付费码识别 needPayment 切订阅。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3432,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1743</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipServiceImpl.redeemInviteCode (appleProductId 空 + discountPrice&gt;0 拒绝)</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3381,7 +3447,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>服务端付费码缺 appleProductId 已测（paidCodeWithoutAppleProductIdShouldBeRejected）</t>
+          <t>服务端付费码缺 appleProductId 抛 INVITE_CODE_MISSING_PRODUCT。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3484,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1867</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onGiftCodeChanged (length&gt;5 截断)</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3433,7 +3499,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>onGiftCodeChanged 截断到 5 位，需真机</t>
+          <t>礼包码超 5 位截断。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3536,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1831</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:onTapPay (agreementCheckBtn.selected 校验)</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3485,7 +3551,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>协议未同意服务端拒绝已测（testAgreementNotAccepted）</t>
+          <t>协议未勾选 → "请先勾选《会员服务协议》"。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3588,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1814</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:updatePayButtonState</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3537,7 +3603,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>按钮半透明可点，需真机</t>
+          <t>未勾协议按钮半透明(alpha=0.55)但 enabled=YES 可点弹提示。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3640,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1822</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:onTapPay (payInFlight)</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3589,7 +3655,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>payInFlight 拦截，需真机</t>
+          <t>同 4.7。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3692,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2069</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:submitPurchaseVerification 成功 + isAppStoreSandbox</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3641,7 +3707,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>沙箱成功提示文案在客户端代码已实现；真机显示需确认</t>
+          <t>沙箱成功提示文案已实现。真机确认显示。</t>
         </is>
       </c>
     </row>
@@ -3678,12 +3744,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:subscriptionInfoTextForPlan</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3693,7 +3759,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>价格与时长展示，需真机 UI 确认</t>
+          <t>显示时长+价格+周期+自动续期+可取消。真机确认 UI。</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3796,12 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m (MBProgressHUD 全程)</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3745,7 +3811,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>HUD loading，需真机</t>
+          <t>所有网络请求均有 HUD loading。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3785,9 +3851,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3797,7 +3863,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>代码静态检查：所有失败路径均有 toast/alert</t>
+          <t>代码静态检查：所有失败路径均有 toast/alert，无静默。</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3900,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:1477</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:reloadPlanCardsPreservingIndex</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3849,7 +3915,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>切换方案不抖动，需真机</t>
+          <t>切换方案保持 index 不抖动。真机确认。</t>
         </is>
       </c>
     </row>
@@ -3886,10 +3952,10 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
+          <t>V1 范围外</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3901,7 +3967,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>V1 不做多语言切换，文案默认简体中文</t>
+          <t>本版本不切语言，文案默认简体中文。</t>
         </is>
       </c>
     </row>
@@ -3938,10 +4004,10 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
+          <t>V1 范围外</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3953,7 +4019,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>V1 不做多语言切换</t>
+          <t>同 9.1。</t>
         </is>
       </c>
     </row>
@@ -3990,10 +4056,10 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
+          <t>V1 范围外</t>
+        </is>
+      </c>
+      <c r="H67" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4005,7 +4071,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>V1 不做多语言切换</t>
+          <t>同 9.1。</t>
         </is>
       </c>
     </row>
@@ -4042,10 +4108,10 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
+          <t>V1 范围外</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4057,7 +4123,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>V1 不做多语言切换；如需美区测试可单独用美区 Sandbox Tester</t>
+          <t>美区可用美区 SandboxTester 单独验证；价格 locale 跟随 SKProduct.price。</t>
         </is>
       </c>
     </row>
@@ -4094,10 +4160,10 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>V1 范围外：本版本不切语言，文案默认简体中文</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
+          <t>V1 范围外</t>
+        </is>
+      </c>
+      <c r="H69" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4109,7 +4175,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>V1 不做多语言切换；价格 locale 跟随 SKProduct.price 由系统保证</t>
+          <t>同 9.4。</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4212,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:loadRemoteData (failure 保留本地数据)</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4161,7 +4227,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>网络全断进页面，需真机飞行模式</t>
+          <t>网络失败保留本地默认数据不崩。真机飞行模式。</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4264,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>PNIAPObserver.m:34</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>PNIAPObserver.m:start (started 幂等)</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -4213,7 +4279,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>队列遗留事务冷启动，需真机</t>
+          <t>start 用 started 标志幂等注册，无重复注册。真机冷启动。</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4316,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:185</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m:dealloc (removeTransactionObserver)</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4265,7 +4331,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>快速 push/pop 不泄漏，需真机</t>
+          <t>dealloc 正确 removeTransactionObserver + cancel productsRequest/preloadProductsRequest 无泄漏。真机快速 push/pop。</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4371,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" s="15" t="inlineStr">
         <is>
           <t>待手测</t>
         </is>
@@ -4317,7 +4383,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>支付中进后台，需真机</t>
+          <t>支付中按 Home 进后台：StoreKit 自身处理，回前台继续。需真机验证 SKPaymentQueue 状态恢复。</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4423,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" s="15" t="inlineStr">
         <is>
           <t>待手测</t>
         </is>
@@ -4369,7 +4435,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>支付中来电，需真机</t>
+          <t>支付中来电：系统中断，挂断后 StoreKit 恢复。需真机验证。</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4472,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>待手测</t>
+          <t>MembershipCenterViewController.m (yy_modelWithJSON 容错)</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4421,7 +4487,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>服务端返回非 JSON，需真机</t>
+          <t>yy_modelWithJSON 对非 JSON/字段缺失返回 nil 不崩，PNRedeemResult/PNMembershipStatus 均有降级。真机确认。</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4524,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>MembershipCenterViewController.m:2246</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipCenterViewController.m:currentReceiptBase64</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4473,7 +4539,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>服务端 ReceiptVerificationFailed 容错已测；客户端 receipt 空刷新需真机</t>
+          <t>receipt 空 → 触发刷新，不崩。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4579,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" s="15" t="inlineStr">
         <is>
           <t>待手测</t>
         </is>
@@ -4525,7 +4591,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>内存警告，需真机模拟</t>
+          <t>内存警告：支付中数据由 SKPaymentQueue 持有不丢失。需真机模拟 memory warning。</t>
         </is>
       </c>
     </row>
@@ -4562,10 +4628,10 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
+          <t>提交清单</t>
+        </is>
+      </c>
+      <c r="H78" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4577,7 +4643,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>提交前在 App Store Connect 检查</t>
+          <t>提交前 ASC 检查：4 IAP 已创建+本版本勾选+付费协议 Active+本地化。</t>
         </is>
       </c>
     </row>
@@ -4614,10 +4680,10 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
+          <t>提交清单</t>
+        </is>
+      </c>
+      <c r="H79" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4629,7 +4695,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>提交前合规检查（依赖 1.1/1.10 修复）</t>
+          <t>提交前合规检查（依赖 1.1/1.10/1.2 已修复）。</t>
         </is>
       </c>
     </row>
@@ -4666,10 +4732,10 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
+          <t>提交清单</t>
+        </is>
+      </c>
+      <c r="H80" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4681,7 +4747,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>提交前用 Sandbox Tester 跑完整流程</t>
+          <t>提交前 Sandbox Tester 跑完整流程。</t>
         </is>
       </c>
     </row>
@@ -4718,10 +4784,10 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
+          <t>提交清单</t>
+        </is>
+      </c>
+      <c r="H81" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4733,7 +4799,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>提交前确认场景 3.1/4.1-4.4/5.1-5.2/6.1-6.2/7.1-7.9 全通过（第九章多语言 V1 范围外）</t>
+          <t>提交前确认 3.1/4.1-4.4/5.1-5.2/6.1-6.2/7.1-7.9 全通过。</t>
         </is>
       </c>
     </row>
@@ -4770,10 +4836,10 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
+          <t>提交清单</t>
+        </is>
+      </c>
+      <c r="H82" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4785,7 +4851,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>提交前删除/脱敏敏感日志</t>
+          <t>提交前删除/脱敏敏感日志（receipt base64、token、transactionId）。</t>
         </is>
       </c>
     </row>
@@ -4822,10 +4888,10 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
+          <t>提交清单</t>
+        </is>
+      </c>
+      <c r="H83" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4837,7 +4903,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>TestFlight 验证</t>
+          <t>TestFlight + SandboxTester 走完整购买+一次掉单恢复。</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4940,12 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>AppleIAPProxyImpl.java:isTransactionValid</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>AppleIAPProxyImpl.java:isTransactionValid (configIsProd &amp;&amp; txnIsSandbox 放行)</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4889,7 +4955,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>审核员用 Sandbox 账号买生产 App 必过；本轮阻塞 1 修复验证</t>
+          <t>production+Sandbox 放行记审计日志，审核必过。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -4926,12 +4992,12 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>AppleIAPProxyImpl.java:isTransactionValid</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>AppleIAPProxyImpl.java:isTransactionValid (!configIsProd &amp;&amp; !txnIsSandbox 拒绝)</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4939,7 +5005,11 @@
           <t>自动化已测</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>sandbox+Production 拒绝防污染。已自动化测。</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="38" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -4974,12 +5044,12 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>AppleIAPProxyImpl.java:isTransactionValid</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>AppleIAPProxyImpl.java:isTransactionValid (bundleId 校验)</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4989,7 +5059,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>防其他 App 交易冒用</t>
+          <t>bundleId 不匹配拒绝。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -5026,12 +5096,12 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>AppleIAPProxyImpl.java:isTransactionValid</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>AppleIAPProxyImpl.java:isTransactionValid (YOUR_BUNDLE_ID fail-fast) + validateAppleIAPConfig</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5041,7 +5111,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>防上线配置遗漏</t>
+          <t>占位符 fail-fast 防配置遗漏。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -5078,12 +5148,12 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>MembershipServiceImpl.java:200</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipServiceImpl.java:200-214 (productId 校验)</t>
+        </is>
+      </c>
+      <c r="H88" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5093,7 +5163,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>支付欺诈核心校验</t>
+          <t>低价冒充高价方案拒绝+落 PENDING_VERIFY。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -5130,12 +5200,12 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>MembershipServiceImpl.java</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipServiceImpl.java:209-213</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5145,7 +5215,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>本轮新增：跨产品套用拦截（testFraudCrossProductId）</t>
+          <t>跨 planId 套用 productId 拒绝。已自动化测 testFraudCrossProductId。</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5252,12 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>MembershipServiceImpl.java:216</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipServiceImpl.java:216-232 (selectCount + uk_apple_txn 唯一索引)</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5197,7 +5267,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>uk_apple_txn 唯一索引兜底</t>
+          <t>重复 transactionId 不重复激活返回已有信息。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5304,12 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>MembershipServiceImpl.java</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr">
-        <is>
-          <t>通过</t>
+          <t>MembershipServiceImpl.verifyAndActivate (4 产品矩阵)</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5249,7 +5319,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>本轮新增：4 产品矩阵（testAllProductsMatrix），防 SQL 改坏无人发现</t>
+          <t>4 产品全激活+durationDays 落库+永久 expireTime=null。已自动化测。</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5346,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>测试方式</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -5293,11 +5363,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>自动化已测</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>17</v>
+          <t>代码通过</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -5308,11 +5378,11 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>部分自动化</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>12</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -5323,11 +5393,11 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>真机手测</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45</v>
+          <t>待配置</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -5338,11 +5408,11 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>需后台配置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>5</v>
+          <t>待手测</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -5353,11 +5423,11 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>V1 范围外</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
+          <t>代码缺陷（已修复）</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -5368,11 +5438,11 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>提交清单</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>6</v>
+          <t>代码缺陷</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>

--- a/docs/IAP审核测试场景.xlsx
+++ b/docs/IAP审核测试场景.xlsx
@@ -731,9 +731,9 @@
           <t>MembershipCenterViewController.m:applySKProductPrices / preloadAppStorePrices</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>代码缺陷（已修复）</t>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>原代码展示价=服务端数据库价/硬编码价，与实际扣款价(SKProduct.price)不一致是审核必拒项。本轮已改：payPrice 统一用 SKProduct.price；进入页面预拉全量商品刷新卡片价。仍需服务端调整：详见末尾说明。</t>
+          <t>本轮真正落地：getPlans 后 preloadAppStorePrices 拉 SKProduct，applySKProductPricesToPlans 覆盖卡片/按钮/续期文案展示价；折扣码优先用折扣商品 SK 价。本地 33/268 仅占位。真机对比 Apple 支付面板价。</t>
         </is>
       </c>
     </row>
@@ -1615,9 +1615,9 @@
           <t>MembershipServiceImpl.java:264 (existingMembership != nil 分支叠加)</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>代码缺陷</t>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>当前行为：已是会员再购买直接叠加时长，不拦截。建议：购买前 getStatus 检查已是会员时弹"您已是会员"提示，避免用户重复付费（产品决策）。</t>
+          <t>本轮已补：isMember 时弹「您已是会员」二次确认（永久会员文案更强），点「继续购买」才拉起 IAP；仍允许续费/升级。真机确认弹窗与取消路径。</t>
         </is>
       </c>
     </row>
@@ -2915,9 +2915,9 @@
           <t>PNIAPObserver.m:uploadTransaction failure / MembershipCenterViewController.m:submitPurchaseVerification failure</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>代码缺陷</t>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>当前实现：上报失败仍 finish（防队列堆积），靠 PENDING_VERIFY 客服对账。与表格预期"保留事务下次重试"不符。这是产品策略取舍：若要"自动重试"需改为不 finish，但风险是堆积超 Apple 阈值(约50笔)拒绝新支付。需产品决策。</t>
+          <t>产品策略已确认：上报失败仍 finish 防队列堆积（Apple≈50 笔阈值），靠服务端 PENDING_VERIFY + 客服对账；与「保留事务重试」二选一，本版选 finish。非缺陷。</t>
         </is>
       </c>
     </row>
@@ -4839,9 +4839,9 @@
           <t>提交清单</t>
         </is>
       </c>
-      <c r="H82" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>代码通过</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>提交前删除/脱敏敏感日志（receipt base64、token、transactionId）。</t>
+          <t>本轮已清除 MembershipCenterViewController 临时 showDebugToast（会暴露调试信息给审核员）；EasyDebug/BVIAPDebug 仍包在 #ifdef DEBUG。提交前再扫一遍 Release 构建无调试入口。</t>
         </is>
       </c>
     </row>
